--- a/research/traditional_assets/database/data/bermuda/bermuda_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0526</v>
+        <v>0.0364</v>
       </c>
       <c r="E2">
-        <v>0.158</v>
+        <v>0.0536</v>
       </c>
       <c r="F2">
         <v>0.06</v>
@@ -603,91 +603,82 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.003162317270050123</v>
+        <v>0.001138145213995111</v>
       </c>
       <c r="J2">
-        <v>-0.003116267816147883</v>
+        <v>0.001116460735643905</v>
       </c>
       <c r="K2">
-        <v>163.1</v>
+        <v>192.6</v>
       </c>
       <c r="L2">
-        <v>0.3269847634322374</v>
+        <v>0.3654648956356736</v>
       </c>
       <c r="M2">
-        <v>105.1</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="N2">
-        <v>0.05653881327666899</v>
+        <v>0.06780939321220432</v>
       </c>
       <c r="O2">
-        <v>0.6443899448191294</v>
+        <v>0.5134994807892005</v>
       </c>
       <c r="P2">
-        <v>87.3</v>
+        <v>87.2</v>
       </c>
       <c r="Q2">
-        <v>0.04696325784065845</v>
+        <v>0.05978745286253</v>
       </c>
       <c r="R2">
-        <v>0.5352544451256898</v>
+        <v>0.4527518172377986</v>
       </c>
       <c r="S2">
-        <v>17.8</v>
+        <v>11.7</v>
       </c>
       <c r="T2">
-        <v>0.1693625118934348</v>
+        <v>0.1183013144590496</v>
       </c>
       <c r="U2">
-        <v>2855.8</v>
+        <v>1993.4</v>
       </c>
       <c r="V2">
-        <v>1.536284899671849</v>
+        <v>1.366746657524854</v>
       </c>
       <c r="W2">
-        <v>0.1649307311153807</v>
+        <v>0.1977615771639799</v>
       </c>
       <c r="X2">
-        <v>0.04715812768160962</v>
+        <v>0.07630971093305519</v>
       </c>
       <c r="Y2">
-        <v>0.1177726034337711</v>
-      </c>
-      <c r="Z2">
-        <v>-0.34347574214261</v>
-      </c>
-      <c r="AA2">
-        <v>0.001070362400866525</v>
+        <v>0.1214518662309247</v>
       </c>
       <c r="AB2">
-        <v>0.04598704670165564</v>
-      </c>
-      <c r="AC2">
-        <v>-0.04491668430078911</v>
+        <v>0.07514654188141605</v>
       </c>
       <c r="AD2">
-        <v>175.6</v>
+        <v>177.6</v>
       </c>
       <c r="AE2">
-        <v>49.48681927150501</v>
+        <v>37.35098736112288</v>
       </c>
       <c r="AF2">
-        <v>225.086819271505</v>
+        <v>214.9509873611229</v>
       </c>
       <c r="AG2">
-        <v>-2630.713180728495</v>
+        <v>-1778.449012638877</v>
       </c>
       <c r="AH2">
-        <v>0.1080077940944886</v>
+        <v>0.1284477340445331</v>
       </c>
       <c r="AI2">
-        <v>0.1877308537955955</v>
+        <v>0.2216330035874739</v>
       </c>
       <c r="AJ2">
-        <v>3.40848439287527</v>
+        <v>5.558538837080869</v>
       </c>
       <c r="AK2">
-        <v>1.587815217387261</v>
+        <v>1.737531853070469</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +687,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>21.10576923076923</v>
+        <v>22.00743494423792</v>
       </c>
       <c r="AP2">
-        <v>-316.1914880683287</v>
+        <v>-220.3778206491793</v>
       </c>
     </row>
     <row r="3">
@@ -719,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0526</v>
+        <v>0.0364</v>
       </c>
       <c r="E3">
-        <v>0.158</v>
+        <v>0.0536</v>
       </c>
       <c r="F3">
         <v>0.06</v>
@@ -734,91 +725,82 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-0.003162317270050123</v>
+        <v>0.001138145213995111</v>
       </c>
       <c r="J3">
-        <v>-0.003116267816147883</v>
+        <v>0.001116460735643905</v>
       </c>
       <c r="K3">
-        <v>163.1</v>
+        <v>192.6</v>
       </c>
       <c r="L3">
-        <v>0.3269847634322374</v>
+        <v>0.3654648956356736</v>
       </c>
       <c r="M3">
-        <v>105.1</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="N3">
-        <v>0.05653881327666899</v>
+        <v>0.06780939321220432</v>
       </c>
       <c r="O3">
-        <v>0.6443899448191294</v>
+        <v>0.5134994807892005</v>
       </c>
       <c r="P3">
-        <v>87.3</v>
+        <v>87.2</v>
       </c>
       <c r="Q3">
-        <v>0.04696325784065845</v>
+        <v>0.05978745286253</v>
       </c>
       <c r="R3">
-        <v>0.5352544451256898</v>
+        <v>0.4527518172377986</v>
       </c>
       <c r="S3">
-        <v>17.8</v>
+        <v>11.7</v>
       </c>
       <c r="T3">
-        <v>0.1693625118934348</v>
+        <v>0.1183013144590496</v>
       </c>
       <c r="U3">
-        <v>2855.8</v>
+        <v>1993.4</v>
       </c>
       <c r="V3">
-        <v>1.536284899671849</v>
+        <v>1.366746657524854</v>
       </c>
       <c r="W3">
-        <v>0.1649307311153807</v>
+        <v>0.1977615771639799</v>
       </c>
       <c r="X3">
-        <v>0.04715812768160962</v>
+        <v>0.07630971093305519</v>
       </c>
       <c r="Y3">
-        <v>0.1177726034337711</v>
-      </c>
-      <c r="Z3">
-        <v>-0.34347574214261</v>
-      </c>
-      <c r="AA3">
-        <v>0.001070362400866525</v>
+        <v>0.1214518662309247</v>
       </c>
       <c r="AB3">
-        <v>0.04598704670165564</v>
-      </c>
-      <c r="AC3">
-        <v>-0.04491668430078911</v>
+        <v>0.07514654188141605</v>
       </c>
       <c r="AD3">
-        <v>175.6</v>
+        <v>177.6</v>
       </c>
       <c r="AE3">
-        <v>49.48681927150501</v>
+        <v>37.35098736112288</v>
       </c>
       <c r="AF3">
-        <v>225.086819271505</v>
+        <v>214.9509873611229</v>
       </c>
       <c r="AG3">
-        <v>-2630.713180728495</v>
+        <v>-1778.449012638877</v>
       </c>
       <c r="AH3">
-        <v>0.1080077940944886</v>
+        <v>0.1284477340445331</v>
       </c>
       <c r="AI3">
-        <v>0.1877308537955955</v>
+        <v>0.2216330035874739</v>
       </c>
       <c r="AJ3">
-        <v>3.40848439287527</v>
+        <v>5.558538837080869</v>
       </c>
       <c r="AK3">
-        <v>1.587815217387261</v>
+        <v>1.737531853070469</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -827,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>21.10576923076923</v>
+        <v>22.00743494423792</v>
       </c>
       <c r="AP3">
-        <v>-316.1914880683287</v>
+        <v>-220.3778206491793</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bermuda/bermuda_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_bank_money_center.xlsx
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0364</v>
+        <v>0.0291</v>
       </c>
       <c r="E2">
-        <v>0.0536</v>
-      </c>
-      <c r="F2">
-        <v>0.06</v>
+        <v>0.0496</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,82 +600,82 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.001138145213995111</v>
+        <v>0.001181272404617103</v>
       </c>
       <c r="J2">
-        <v>0.001116460735643905</v>
+        <v>0.001169872852124169</v>
       </c>
       <c r="K2">
-        <v>192.6</v>
+        <v>235.1</v>
       </c>
       <c r="L2">
-        <v>0.3654648956356736</v>
+        <v>0.4038131226382686</v>
       </c>
       <c r="M2">
-        <v>98.90000000000001</v>
+        <v>142.1</v>
       </c>
       <c r="N2">
-        <v>0.06780939321220432</v>
+        <v>0.09235068564372521</v>
       </c>
       <c r="O2">
-        <v>0.5134994807892005</v>
+        <v>0.6044236495108465</v>
       </c>
       <c r="P2">
-        <v>87.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Q2">
-        <v>0.05978745286253</v>
+        <v>0.05660622603496458</v>
       </c>
       <c r="R2">
-        <v>0.4527518172377986</v>
+        <v>0.37048064653339</v>
       </c>
       <c r="S2">
-        <v>11.7</v>
+        <v>55</v>
       </c>
       <c r="T2">
-        <v>0.1183013144590496</v>
+        <v>0.3870513722730471</v>
       </c>
       <c r="U2">
-        <v>1993.4</v>
+        <v>2118</v>
       </c>
       <c r="V2">
-        <v>1.366746657524854</v>
+        <v>1.376486644570092</v>
       </c>
       <c r="W2">
-        <v>0.1977615771639799</v>
+        <v>0.3114319777453968</v>
       </c>
       <c r="X2">
-        <v>0.07630971093305519</v>
+        <v>0.06377600200251113</v>
       </c>
       <c r="Y2">
-        <v>0.1214518662309247</v>
+        <v>0.2476559757428856</v>
       </c>
       <c r="AB2">
-        <v>0.07514654188141605</v>
+        <v>0.06358669467280458</v>
       </c>
       <c r="AD2">
-        <v>177.6</v>
+        <v>101.5</v>
       </c>
       <c r="AE2">
-        <v>37.35098736112288</v>
+        <v>32.21131603015962</v>
       </c>
       <c r="AF2">
-        <v>214.9509873611229</v>
+        <v>133.7113160301596</v>
       </c>
       <c r="AG2">
-        <v>-1778.449012638877</v>
+        <v>-1984.28868396984</v>
       </c>
       <c r="AH2">
-        <v>0.1284477340445331</v>
+        <v>0.07995121460165265</v>
       </c>
       <c r="AI2">
-        <v>0.2216330035874739</v>
+        <v>0.126547306470777</v>
       </c>
       <c r="AJ2">
-        <v>5.558538837080869</v>
+        <v>4.453184641700073</v>
       </c>
       <c r="AK2">
-        <v>1.737531853070469</v>
+        <v>1.869521235659061</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -687,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>22.00743494423792</v>
+        <v>14.23562412342216</v>
       </c>
       <c r="AP2">
-        <v>-220.3778206491793</v>
+        <v>-278.3013582005386</v>
       </c>
     </row>
     <row r="3">
@@ -710,13 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0364</v>
+        <v>0.0291</v>
       </c>
       <c r="E3">
-        <v>0.0536</v>
-      </c>
-      <c r="F3">
-        <v>0.06</v>
+        <v>0.0496</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,82 +719,82 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.001138145213995111</v>
+        <v>0.001181272404617103</v>
       </c>
       <c r="J3">
-        <v>0.001116460735643905</v>
+        <v>0.001169872852124169</v>
       </c>
       <c r="K3">
-        <v>192.6</v>
+        <v>235.1</v>
       </c>
       <c r="L3">
-        <v>0.3654648956356736</v>
+        <v>0.4038131226382686</v>
       </c>
       <c r="M3">
-        <v>98.90000000000001</v>
+        <v>142.1</v>
       </c>
       <c r="N3">
-        <v>0.06780939321220432</v>
+        <v>0.09235068564372521</v>
       </c>
       <c r="O3">
-        <v>0.5134994807892005</v>
+        <v>0.6044236495108465</v>
       </c>
       <c r="P3">
-        <v>87.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.05978745286253</v>
+        <v>0.05660622603496458</v>
       </c>
       <c r="R3">
-        <v>0.4527518172377986</v>
+        <v>0.37048064653339</v>
       </c>
       <c r="S3">
-        <v>11.7</v>
+        <v>55</v>
       </c>
       <c r="T3">
-        <v>0.1183013144590496</v>
+        <v>0.3870513722730471</v>
       </c>
       <c r="U3">
-        <v>1993.4</v>
+        <v>2118</v>
       </c>
       <c r="V3">
-        <v>1.366746657524854</v>
+        <v>1.376486644570092</v>
       </c>
       <c r="W3">
-        <v>0.1977615771639799</v>
+        <v>0.3114319777453968</v>
       </c>
       <c r="X3">
-        <v>0.07630971093305519</v>
+        <v>0.06377600200251113</v>
       </c>
       <c r="Y3">
-        <v>0.1214518662309247</v>
+        <v>0.2476559757428856</v>
       </c>
       <c r="AB3">
-        <v>0.07514654188141605</v>
+        <v>0.06358669467280458</v>
       </c>
       <c r="AD3">
-        <v>177.6</v>
+        <v>101.5</v>
       </c>
       <c r="AE3">
-        <v>37.35098736112288</v>
+        <v>32.21131603015962</v>
       </c>
       <c r="AF3">
-        <v>214.9509873611229</v>
+        <v>133.7113160301596</v>
       </c>
       <c r="AG3">
-        <v>-1778.449012638877</v>
+        <v>-1984.28868396984</v>
       </c>
       <c r="AH3">
-        <v>0.1284477340445331</v>
+        <v>0.07995121460165265</v>
       </c>
       <c r="AI3">
-        <v>0.2216330035874739</v>
+        <v>0.126547306470777</v>
       </c>
       <c r="AJ3">
-        <v>5.558538837080869</v>
+        <v>4.453184641700073</v>
       </c>
       <c r="AK3">
-        <v>1.737531853070469</v>
+        <v>1.869521235659061</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -809,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>22.00743494423792</v>
+        <v>14.23562412342216</v>
       </c>
       <c r="AP3">
-        <v>-220.3778206491793</v>
+        <v>-278.3013582005386</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bermuda/bermuda_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_bank_money_center.xlsx
@@ -588,10 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0291</v>
+        <v>0.0153</v>
       </c>
       <c r="E2">
-        <v>0.0496</v>
+        <v>0.027</v>
+      </c>
+      <c r="F2">
+        <v>0.06</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,82 +603,82 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.001181272404617103</v>
+        <v>0.001454959302012289</v>
       </c>
       <c r="J2">
-        <v>0.001169872852124169</v>
+        <v>0.00143969078792529</v>
       </c>
       <c r="K2">
-        <v>235.1</v>
+        <v>210.3</v>
       </c>
       <c r="L2">
-        <v>0.4038131226382686</v>
+        <v>0.3669516663758506</v>
       </c>
       <c r="M2">
-        <v>142.1</v>
+        <v>222.9</v>
       </c>
       <c r="N2">
-        <v>0.09235068564372521</v>
+        <v>0.138061319293899</v>
       </c>
       <c r="O2">
-        <v>0.6044236495108465</v>
+        <v>1.059914407988588</v>
       </c>
       <c r="P2">
-        <v>87.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="Q2">
-        <v>0.05660622603496458</v>
+        <v>0.05035614741406008</v>
       </c>
       <c r="R2">
-        <v>0.37048064653339</v>
+        <v>0.3865905848787446</v>
       </c>
       <c r="S2">
-        <v>55</v>
+        <v>141.6</v>
       </c>
       <c r="T2">
-        <v>0.3870513722730471</v>
+        <v>0.6352624495289366</v>
       </c>
       <c r="U2">
-        <v>2118</v>
+        <v>2305.5</v>
       </c>
       <c r="V2">
-        <v>1.376486644570092</v>
+        <v>1.427996283679158</v>
       </c>
       <c r="W2">
-        <v>0.3114319777453968</v>
+        <v>0.2278686748293423</v>
       </c>
       <c r="X2">
-        <v>0.06377600200251113</v>
+        <v>0.070674811010487</v>
       </c>
       <c r="Y2">
-        <v>0.2476559757428856</v>
+        <v>0.1571938638188553</v>
       </c>
       <c r="AB2">
-        <v>0.06358669467280458</v>
+        <v>0.069875457499192</v>
       </c>
       <c r="AD2">
-        <v>101.5</v>
+        <v>221.7</v>
       </c>
       <c r="AE2">
-        <v>32.21131603015962</v>
+        <v>31.63081412008378</v>
       </c>
       <c r="AF2">
-        <v>133.7113160301596</v>
+        <v>253.3308141200838</v>
       </c>
       <c r="AG2">
-        <v>-1984.28868396984</v>
+        <v>-2052.169185879916</v>
       </c>
       <c r="AH2">
-        <v>0.07995121460165265</v>
+        <v>0.1356283514572091</v>
       </c>
       <c r="AI2">
-        <v>0.126547306470777</v>
+        <v>0.1922769558063592</v>
       </c>
       <c r="AJ2">
-        <v>4.453184641700073</v>
+        <v>4.688859193397663</v>
       </c>
       <c r="AK2">
-        <v>1.869521235659061</v>
+        <v>2.077159100920936</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -684,10 +687,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>14.23562412342216</v>
+        <v>30.96368715083799</v>
       </c>
       <c r="AP2">
-        <v>-278.3013582005386</v>
+        <v>-286.6158080837872</v>
       </c>
     </row>
     <row r="3">
@@ -707,10 +710,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0291</v>
+        <v>0.0153</v>
       </c>
       <c r="E3">
-        <v>0.0496</v>
+        <v>0.027</v>
+      </c>
+      <c r="F3">
+        <v>0.06</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -719,82 +725,82 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.001181272404617103</v>
+        <v>0.001454959302012289</v>
       </c>
       <c r="J3">
-        <v>0.001169872852124169</v>
+        <v>0.00143969078792529</v>
       </c>
       <c r="K3">
-        <v>235.1</v>
+        <v>210.3</v>
       </c>
       <c r="L3">
-        <v>0.4038131226382686</v>
+        <v>0.3669516663758506</v>
       </c>
       <c r="M3">
-        <v>142.1</v>
+        <v>222.9</v>
       </c>
       <c r="N3">
-        <v>0.09235068564372521</v>
+        <v>0.138061319293899</v>
       </c>
       <c r="O3">
-        <v>0.6044236495108465</v>
+        <v>1.059914407988588</v>
       </c>
       <c r="P3">
-        <v>87.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="Q3">
-        <v>0.05660622603496458</v>
+        <v>0.05035614741406008</v>
       </c>
       <c r="R3">
-        <v>0.37048064653339</v>
+        <v>0.3865905848787446</v>
       </c>
       <c r="S3">
-        <v>55</v>
+        <v>141.6</v>
       </c>
       <c r="T3">
-        <v>0.3870513722730471</v>
+        <v>0.6352624495289366</v>
       </c>
       <c r="U3">
-        <v>2118</v>
+        <v>2305.5</v>
       </c>
       <c r="V3">
-        <v>1.376486644570092</v>
+        <v>1.427996283679158</v>
       </c>
       <c r="W3">
-        <v>0.3114319777453968</v>
+        <v>0.2278686748293423</v>
       </c>
       <c r="X3">
-        <v>0.06377600200251113</v>
+        <v>0.070674811010487</v>
       </c>
       <c r="Y3">
-        <v>0.2476559757428856</v>
+        <v>0.1571938638188553</v>
       </c>
       <c r="AB3">
-        <v>0.06358669467280458</v>
+        <v>0.069875457499192</v>
       </c>
       <c r="AD3">
-        <v>101.5</v>
+        <v>221.7</v>
       </c>
       <c r="AE3">
-        <v>32.21131603015962</v>
+        <v>31.63081412008378</v>
       </c>
       <c r="AF3">
-        <v>133.7113160301596</v>
+        <v>253.3308141200838</v>
       </c>
       <c r="AG3">
-        <v>-1984.28868396984</v>
+        <v>-2052.169185879916</v>
       </c>
       <c r="AH3">
-        <v>0.07995121460165265</v>
+        <v>0.1356283514572091</v>
       </c>
       <c r="AI3">
-        <v>0.126547306470777</v>
+        <v>0.1922769558063592</v>
       </c>
       <c r="AJ3">
-        <v>4.453184641700073</v>
+        <v>4.688859193397663</v>
       </c>
       <c r="AK3">
-        <v>1.869521235659061</v>
+        <v>2.077159100920936</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -803,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>14.23562412342216</v>
+        <v>30.96368715083799</v>
       </c>
       <c r="AP3">
-        <v>-278.3013582005386</v>
+        <v>-286.6158080837872</v>
       </c>
     </row>
   </sheetData>
